--- a/artfynd/A 25648-2024 artfynd.xlsx
+++ b/artfynd/A 25648-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123420716</v>
+        <v>123420717</v>
       </c>
       <c r="B2" t="n">
-        <v>79387</v>
+        <v>57497</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,21 +713,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Rismyran SO om, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>597289</v>
+        <v>597394</v>
       </c>
       <c r="R2" t="n">
-        <v>6820171</v>
+        <v>6820178</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +749,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2024_2402</t>
+          <t>2024_2401</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -764,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -805,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123420718</v>
+        <v>123420716</v>
       </c>
       <c r="B3" t="n">
-        <v>78769</v>
+        <v>79389</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -821,21 +816,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -854,10 +849,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>597253</v>
+        <v>597289</v>
       </c>
       <c r="R3" t="n">
-        <v>6820263</v>
+        <v>6820171</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,7 +879,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_2400</t>
+          <t>2024_2402</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -894,7 +889,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +899,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -935,10 +930,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123420717</v>
+        <v>123420718</v>
       </c>
       <c r="B4" t="n">
-        <v>57497</v>
+        <v>78771</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -951,21 +946,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -973,16 +968,21 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Rismyran SO om, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>597394</v>
+        <v>597253</v>
       </c>
       <c r="R4" t="n">
-        <v>6820178</v>
+        <v>6820263</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024_2401</t>
+          <t>2024_2400</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 25648-2024 artfynd.xlsx
+++ b/artfynd/A 25648-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123420717</v>
+        <v>123420718</v>
       </c>
       <c r="B2" t="n">
-        <v>57497</v>
+        <v>78772</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,16 +713,21 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Rismyran SO om, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>597394</v>
+        <v>597253</v>
       </c>
       <c r="R2" t="n">
-        <v>6820178</v>
+        <v>6820263</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,7 +754,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2024_2401</t>
+          <t>2024_2400</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -759,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +774,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -800,10 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123420716</v>
+        <v>123420717</v>
       </c>
       <c r="B3" t="n">
-        <v>79389</v>
+        <v>57497</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -816,21 +821,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -838,21 +843,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Rismyran SO om, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>597289</v>
+        <v>597394</v>
       </c>
       <c r="R3" t="n">
-        <v>6820171</v>
+        <v>6820178</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,7 +879,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_2402</t>
+          <t>2024_2401</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -930,10 +930,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123420718</v>
+        <v>123420716</v>
       </c>
       <c r="B4" t="n">
-        <v>78771</v>
+        <v>79390</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -946,21 +946,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -979,10 +979,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>597253</v>
+        <v>597289</v>
       </c>
       <c r="R4" t="n">
-        <v>6820263</v>
+        <v>6820171</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024_2400</t>
+          <t>2024_2402</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 25648-2024 artfynd.xlsx
+++ b/artfynd/A 25648-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123420718</v>
+        <v>123420716</v>
       </c>
       <c r="B2" t="n">
-        <v>78775</v>
+        <v>79399</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>597253</v>
+        <v>597289</v>
       </c>
       <c r="R2" t="n">
-        <v>6820263</v>
+        <v>6820171</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2024_2400</t>
+          <t>2024_2402</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -808,7 +808,7 @@
         <v>123420717</v>
       </c>
       <c r="B3" t="n">
-        <v>57497</v>
+        <v>57503</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -930,10 +930,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123420716</v>
+        <v>123420718</v>
       </c>
       <c r="B4" t="n">
-        <v>79393</v>
+        <v>78781</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -946,21 +946,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -979,10 +979,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>597289</v>
+        <v>597253</v>
       </c>
       <c r="R4" t="n">
-        <v>6820171</v>
+        <v>6820263</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024_2402</t>
+          <t>2024_2400</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 25648-2024 artfynd.xlsx
+++ b/artfynd/A 25648-2024 artfynd.xlsx
@@ -805,10 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123420717</v>
+        <v>123420718</v>
       </c>
       <c r="B3" t="n">
-        <v>57503</v>
+        <v>78781</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -821,21 +821,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -843,16 +843,21 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Rismyran SO om, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>597394</v>
+        <v>597253</v>
       </c>
       <c r="R3" t="n">
-        <v>6820178</v>
+        <v>6820263</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,7 +884,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_2401</t>
+          <t>2024_2400</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -889,7 +894,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -899,7 +904,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -930,10 +935,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123420718</v>
+        <v>123420717</v>
       </c>
       <c r="B4" t="n">
-        <v>78781</v>
+        <v>57503</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -946,21 +951,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -968,21 +973,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Rismyran SO om, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>597253</v>
+        <v>597394</v>
       </c>
       <c r="R4" t="n">
-        <v>6820263</v>
+        <v>6820178</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024_2400</t>
+          <t>2024_2401</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 25648-2024 artfynd.xlsx
+++ b/artfynd/A 25648-2024 artfynd.xlsx
@@ -805,10 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123420718</v>
+        <v>123420717</v>
       </c>
       <c r="B3" t="n">
-        <v>78781</v>
+        <v>57503</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -821,21 +821,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -843,21 +843,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Rismyran SO om, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>597253</v>
+        <v>597394</v>
       </c>
       <c r="R3" t="n">
-        <v>6820263</v>
+        <v>6820178</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,7 +879,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_2400</t>
+          <t>2024_2401</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -894,7 +889,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +899,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -935,10 +930,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123420717</v>
+        <v>123420718</v>
       </c>
       <c r="B4" t="n">
-        <v>57503</v>
+        <v>78781</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -951,21 +946,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -973,16 +968,21 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Rismyran SO om, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>597394</v>
+        <v>597253</v>
       </c>
       <c r="R4" t="n">
-        <v>6820178</v>
+        <v>6820263</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024_2401</t>
+          <t>2024_2400</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 25648-2024 artfynd.xlsx
+++ b/artfynd/A 25648-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123420716</v>
       </c>
       <c r="B2" t="n">
-        <v>79399</v>
+        <v>79404</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -805,10 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123420717</v>
+        <v>123420718</v>
       </c>
       <c r="B3" t="n">
-        <v>57503</v>
+        <v>78786</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -821,21 +821,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -843,16 +843,21 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Rismyran SO om, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>597394</v>
+        <v>597253</v>
       </c>
       <c r="R3" t="n">
-        <v>6820178</v>
+        <v>6820263</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,7 +884,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_2401</t>
+          <t>2024_2400</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -889,7 +894,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -899,7 +904,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -930,10 +935,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123420718</v>
+        <v>123420717</v>
       </c>
       <c r="B4" t="n">
-        <v>78781</v>
+        <v>57506</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -946,21 +951,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -968,21 +973,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Rismyran SO om, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>597253</v>
+        <v>597394</v>
       </c>
       <c r="R4" t="n">
-        <v>6820263</v>
+        <v>6820178</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024_2400</t>
+          <t>2024_2401</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 25648-2024 artfynd.xlsx
+++ b/artfynd/A 25648-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123420716</v>
+        <v>123420717</v>
       </c>
       <c r="B2" t="n">
-        <v>79404</v>
+        <v>57507</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,21 +713,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Rismyran SO om, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>597289</v>
+        <v>597394</v>
       </c>
       <c r="R2" t="n">
-        <v>6820171</v>
+        <v>6820178</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +749,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2024_2402</t>
+          <t>2024_2401</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -764,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -808,7 +803,7 @@
         <v>123420718</v>
       </c>
       <c r="B3" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -935,10 +930,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123420717</v>
+        <v>123420716</v>
       </c>
       <c r="B4" t="n">
-        <v>57506</v>
+        <v>79406</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -951,21 +946,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -973,16 +968,21 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Rismyran SO om, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>597394</v>
+        <v>597289</v>
       </c>
       <c r="R4" t="n">
-        <v>6820178</v>
+        <v>6820171</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024_2401</t>
+          <t>2024_2402</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 25648-2024 artfynd.xlsx
+++ b/artfynd/A 25648-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123420717</v>
+        <v>123420716</v>
       </c>
       <c r="B2" t="n">
-        <v>57507</v>
+        <v>79406</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,16 +713,21 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Rismyran SO om, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>597394</v>
+        <v>597289</v>
       </c>
       <c r="R2" t="n">
-        <v>6820178</v>
+        <v>6820171</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,7 +754,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2024_2401</t>
+          <t>2024_2402</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -759,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +774,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -800,10 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123420718</v>
+        <v>123420717</v>
       </c>
       <c r="B3" t="n">
-        <v>78788</v>
+        <v>57507</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -816,21 +821,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -838,21 +843,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Rismyran SO om, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>597253</v>
+        <v>597394</v>
       </c>
       <c r="R3" t="n">
-        <v>6820263</v>
+        <v>6820178</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,7 +879,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_2400</t>
+          <t>2024_2401</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -930,10 +930,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123420716</v>
+        <v>123420718</v>
       </c>
       <c r="B4" t="n">
-        <v>79406</v>
+        <v>78788</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -946,21 +946,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -979,10 +979,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>597289</v>
+        <v>597253</v>
       </c>
       <c r="R4" t="n">
-        <v>6820171</v>
+        <v>6820263</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024_2402</t>
+          <t>2024_2400</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 25648-2024 artfynd.xlsx
+++ b/artfynd/A 25648-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123420716</v>
+        <v>123420718</v>
       </c>
       <c r="B2" t="n">
-        <v>79406</v>
+        <v>78788</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>597289</v>
+        <v>597253</v>
       </c>
       <c r="R2" t="n">
-        <v>6820171</v>
+        <v>6820263</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2024_2402</t>
+          <t>2024_2400</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -930,10 +930,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123420718</v>
+        <v>123420716</v>
       </c>
       <c r="B4" t="n">
-        <v>78788</v>
+        <v>79406</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -946,21 +946,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -979,10 +979,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>597253</v>
+        <v>597289</v>
       </c>
       <c r="R4" t="n">
-        <v>6820263</v>
+        <v>6820171</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024_2400</t>
+          <t>2024_2402</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 25648-2024 artfynd.xlsx
+++ b/artfynd/A 25648-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123420718</v>
+        <v>123420716</v>
       </c>
       <c r="B2" t="n">
-        <v>78788</v>
+        <v>79406</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>597253</v>
+        <v>597289</v>
       </c>
       <c r="R2" t="n">
-        <v>6820263</v>
+        <v>6820171</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2024_2400</t>
+          <t>2024_2402</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -805,10 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123420717</v>
+        <v>123420718</v>
       </c>
       <c r="B3" t="n">
-        <v>57507</v>
+        <v>78788</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -821,21 +821,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -843,16 +843,21 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Rismyran SO om, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>597394</v>
+        <v>597253</v>
       </c>
       <c r="R3" t="n">
-        <v>6820178</v>
+        <v>6820263</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,7 +884,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_2401</t>
+          <t>2024_2400</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -889,7 +894,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -899,7 +904,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -930,10 +935,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123420716</v>
+        <v>123420717</v>
       </c>
       <c r="B4" t="n">
-        <v>79406</v>
+        <v>57507</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -946,21 +951,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -968,21 +973,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Rismyran SO om, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>597289</v>
+        <v>597394</v>
       </c>
       <c r="R4" t="n">
-        <v>6820171</v>
+        <v>6820178</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024_2402</t>
+          <t>2024_2401</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 25648-2024 artfynd.xlsx
+++ b/artfynd/A 25648-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123420716</v>
+        <v>123420718</v>
       </c>
       <c r="B2" t="n">
-        <v>79406</v>
+        <v>78788</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>597289</v>
+        <v>597253</v>
       </c>
       <c r="R2" t="n">
-        <v>6820171</v>
+        <v>6820263</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2024_2402</t>
+          <t>2024_2400</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -805,10 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123420718</v>
+        <v>123420717</v>
       </c>
       <c r="B3" t="n">
-        <v>78788</v>
+        <v>57507</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -821,21 +821,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -843,21 +843,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Rismyran SO om, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>597253</v>
+        <v>597394</v>
       </c>
       <c r="R3" t="n">
-        <v>6820263</v>
+        <v>6820178</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,7 +879,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_2400</t>
+          <t>2024_2401</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -894,7 +889,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +899,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -935,10 +930,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123420717</v>
+        <v>123420716</v>
       </c>
       <c r="B4" t="n">
-        <v>57507</v>
+        <v>79406</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -951,21 +946,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -973,16 +968,21 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Rismyran SO om, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>597394</v>
+        <v>597289</v>
       </c>
       <c r="R4" t="n">
-        <v>6820178</v>
+        <v>6820171</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024_2401</t>
+          <t>2024_2402</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD4" t="b">
